--- a/jpcore-r4/feature/wg45-familymember-birth-order-label/StructureDefinition-jp-medicationadministrationBase.xlsx
+++ b/jpcore-r4/feature/wg45-familymember-birth-order-label/StructureDefinition-jp-medicationadministrationBase.xlsx
@@ -560,7 +560,7 @@
   <si>
     <t>このインスタンスが外部から参照されるために使われるIDである。処方箋全体としてのIDとしては使用しない。  
 処方箋内で同一の用法をまとめて表記されるRp番号はこのIdentifier elementの別スライスで表現する。それ以外に任意のIDを付与してもよい。  
-このIDは業務手順によって定められた処方オーダに対して、直接的なURL参照が適切でない場合も含めて関連付けるために使われる。この業務手順のIDは実施者によって割り当てられたものであり、リソースが更新されたりサーバからサーバに転送されたとしても固定のものとして存続する。</t>
+このIDは業務手順によって定められた処方オーダに対して、直接的なURL参照が適切でない場合も含めて関連付けるために使われる。この業務手順のIDは実施者によって割り当てられたものであり、リソースが更新されたりサーバーからサーバーに転送されたとしても固定のものとして存続する。</t>
   </si>
   <si>
     <t>これは業務IDであって、リソースに対するIDではない。</t>
